--- a/samples/demo_tender/Pricing Schedule.xlsx
+++ b/samples/demo_tender/Pricing Schedule.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Demolition of existing pavilion</t>
+          <t>Demolition of existing pavilion (asbestos survey not yet carried out)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Piled foundations</t>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,72 +506,1052 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Steel frame</t>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>nr</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Provisional sum: diversion of existing water main</t>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>item</t>
+          <t>nr</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>40000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pile type P4, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Pile type P1, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pile type P2, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pile type P3, 450 mm diameter, bored to 12 m</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>nr</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Steel frame</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Provisional sum: diversion of existing water main</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Contractor's design: mechanical and electrical services (fit for purpose)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D56" t="n">
         <v>1</v>
       </c>
     </row>
